--- a/artfynd/A 35889-2025 artfynd.xlsx
+++ b/artfynd/A 35889-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -913,6 +913,262 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128955168</v>
+      </c>
+      <c r="B4" t="n">
+        <v>87025</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3624</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Strimspindling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Limnäsudden NR, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>516220</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6669088</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>kalkmark</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128955174</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92830</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Limnäsudden NR, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>516169</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6669110</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>kalkmark</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35889-2025 artfynd.xlsx
+++ b/artfynd/A 35889-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>128955168</v>
       </c>
       <c r="B4" t="n">
-        <v>87025</v>
+        <v>87029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>128955174</v>
       </c>
       <c r="B5" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35889-2025 artfynd.xlsx
+++ b/artfynd/A 35889-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>128955168</v>
       </c>
       <c r="B4" t="n">
-        <v>87029</v>
+        <v>87034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>128955174</v>
       </c>
       <c r="B5" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35889-2025 artfynd.xlsx
+++ b/artfynd/A 35889-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>128955168</v>
       </c>
       <c r="B4" t="n">
-        <v>87041</v>
+        <v>87044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>128955174</v>
       </c>
       <c r="B5" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35889-2025 artfynd.xlsx
+++ b/artfynd/A 35889-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>128955168</v>
       </c>
       <c r="B4" t="n">
-        <v>87044</v>
+        <v>87047</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>128955174</v>
       </c>
       <c r="B5" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35889-2025 artfynd.xlsx
+++ b/artfynd/A 35889-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>128955168</v>
       </c>
       <c r="B4" t="n">
-        <v>87047</v>
+        <v>87051</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>128955174</v>
       </c>
       <c r="B5" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35889-2025 artfynd.xlsx
+++ b/artfynd/A 35889-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>128955168</v>
       </c>
       <c r="B4" t="n">
-        <v>87051</v>
+        <v>87058</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>128955174</v>
       </c>
       <c r="B5" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35889-2025 artfynd.xlsx
+++ b/artfynd/A 35889-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>128955168</v>
       </c>
       <c r="B4" t="n">
-        <v>87058</v>
+        <v>87060</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>128955174</v>
       </c>
       <c r="B5" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35889-2025 artfynd.xlsx
+++ b/artfynd/A 35889-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>128955168</v>
       </c>
       <c r="B4" t="n">
-        <v>87060</v>
+        <v>87061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>128955174</v>
       </c>
       <c r="B5" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35889-2025 artfynd.xlsx
+++ b/artfynd/A 35889-2025 artfynd.xlsx
@@ -1048,7 +1048,7 @@
         <v>128955174</v>
       </c>
       <c r="B5" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35889-2025 artfynd.xlsx
+++ b/artfynd/A 35889-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>128955168</v>
       </c>
       <c r="B4" t="n">
-        <v>87061</v>
+        <v>87064</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>128955174</v>
       </c>
       <c r="B5" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35889-2025 artfynd.xlsx
+++ b/artfynd/A 35889-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>128955168</v>
       </c>
       <c r="B4" t="n">
-        <v>87064</v>
+        <v>87066</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>128955174</v>
       </c>
       <c r="B5" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35889-2025 artfynd.xlsx
+++ b/artfynd/A 35889-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>128955168</v>
       </c>
       <c r="B4" t="n">
-        <v>87066</v>
+        <v>87070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>128955174</v>
       </c>
       <c r="B5" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35889-2025 artfynd.xlsx
+++ b/artfynd/A 35889-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>128955168</v>
       </c>
       <c r="B4" t="n">
-        <v>87070</v>
+        <v>87071</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>128955174</v>
       </c>
       <c r="B5" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35889-2025 artfynd.xlsx
+++ b/artfynd/A 35889-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16574683</v>
+        <v>128955168</v>
       </c>
       <c r="B2" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87412</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221725</v>
+        <v>3624</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Limnäsudden vid Plogen, Dlr</t>
+          <t>Limnäsudden NR, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516191.115882598</v>
+        <v>516220</v>
       </c>
       <c r="R2" t="n">
-        <v>6669140.245664977</v>
+        <v>6669088</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,22 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-09-02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-09-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,12 +761,33 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>planterad granskog på kalkmark</t>
+          <t>kalkmark</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -788,22 +798,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Ingela Källén</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16574687</v>
+        <v>67366552</v>
       </c>
       <c r="B3" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92836</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,37 +816,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>4740</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Sotriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius lignyotus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Limnäsudden vid Plogen, Dlr</t>
+          <t>Limnäsudden i Plogen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516191.115882598</v>
+        <v>516234</v>
       </c>
       <c r="R3" t="n">
-        <v>6669140.245664977</v>
+        <v>6669046</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -868,22 +880,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-09-02</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-09-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,12 +894,33 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>planterad granskog på kalkmark</t>
+          <t>kalkamrk</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -908,47 +931,43 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Ingela Källén</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128955168</v>
+        <v>128955174</v>
       </c>
       <c r="B4" t="n">
-        <v>87071</v>
+        <v>93233</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3624</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -957,10 +976,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516220</v>
+        <v>516169</v>
       </c>
       <c r="R4" t="n">
-        <v>6669088</v>
+        <v>6669110</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1045,10 +1064,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128955174</v>
+        <v>16574683</v>
       </c>
       <c r="B5" t="n">
-        <v>92868</v>
+        <v>106229</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,37 +1075,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>221725</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Limnäsudden NR, Dlr</t>
+          <t>Limnäsudden vid Plogen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516169</v>
+        <v>516191</v>
       </c>
       <c r="R5" t="n">
-        <v>6669110</v>
+        <v>6669140</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1113,12 +1132,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2014-09-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2014-09-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,33 +1146,12 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>kalkmark</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>planterad granskog på kalkmark</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1164,10 +1162,115 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
+          <t>Janolof Hermansson, Ingela Källén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>16574687</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Limnäsudden vid Plogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>516191</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6669140</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2014-09-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2014-09-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>planterad granskog på kalkmark</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Janolof Hermansson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Ingela Källén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35889-2025 artfynd.xlsx
+++ b/artfynd/A 35889-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128955168</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -935,6 +945,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67366552</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1061,6 +1076,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128955174</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1166,6 +1186,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16574683</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1271,8 +1296,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16574687</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>